--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:46:53+00:00</t>
+    <t>2025-05-20T13:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:54:28+00:00</t>
+    <t>2025-05-20T13:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:56:00+00:00</t>
+    <t>2025-05-23T16:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:42:05+00:00</t>
+    <t>2025-05-23T16:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:51:26+00:00</t>
+    <t>2025-05-24T07:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-24T07:13:38+00:00</t>
+    <t>2025-05-26T07:36:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T07:36:52+00:00</t>
+    <t>2025-05-28T11:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
